--- a/data/trans_orig/P43A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59540</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59540</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30295</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30295</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>68727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>68727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>108948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>108948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46173</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72161</t>
+          <t>71822</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46173</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72161</t>
+          <t>71822</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42794</t>
+          <t>42448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42794</t>
+          <t>42448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50959</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50959</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67833</t>
+          <t>68973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97032</t>
+          <t>96057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67833</t>
+          <t>68973</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97032</t>
+          <t>96057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50349</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50349</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>137176</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175496</t>
+          <t>176954</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>137176</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175496</t>
+          <t>176954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>143861</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>185198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>143861</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>185198</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>121119</t>
+          <t>122760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>121119</t>
+          <t>122760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69284</t>
+          <t>68846</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101741</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69284</t>
+          <t>68846</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101741</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61249</t>
+          <t>60243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61249</t>
+          <t>60243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -3760,12 +3760,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>30737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52872</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>30737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52872</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -3998,12 +3998,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>33002</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>33002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>33101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>33101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64983</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>87997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121229</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>87997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121229</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>77368</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109565</t>
+          <t>109447</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>77368</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109565</t>
+          <t>109447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>69576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>69576</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>72380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107369</t>
+          <t>108182</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>72380</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107369</t>
+          <t>108182</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134201</t>
+          <t>133129</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173715</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134201</t>
+          <t>133129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173715</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>78110</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113813</t>
+          <t>111812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>78110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113813</t>
+          <t>111812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40929</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>68144</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40929</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>68144</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113359</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>155355</t>
+          <t>153310</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>113359</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155355</t>
+          <t>153310</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>216557</t>
+          <t>217627</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>263757</t>
+          <t>265483</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>216557</t>
+          <t>217627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>263757</t>
+          <t>265483</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110748</t>
+          <t>111982</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>153348</t>
+          <t>153406</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>110748</t>
+          <t>111982</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>153348</t>
+          <t>153406</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>86219</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>86219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -5968,12 +5968,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>306893</t>
+          <t>306924</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>374689</t>
+          <t>375906</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>306893</t>
+          <t>306924</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>374689</t>
+          <t>375906</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>593053</t>
+          <t>594035</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>676139</t>
+          <t>678667</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>593053</t>
+          <t>594035</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>676139</t>
+          <t>678667</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>404045</t>
+          <t>406066</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>479808</t>
+          <t>479233</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>404045</t>
+          <t>406066</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>479808</t>
+          <t>479233</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>212535</t>
+          <t>212593</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>273729</t>
+          <t>272746</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>212535</t>
+          <t>212593</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>273729</t>
+          <t>272746</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87332</t>
+          <t>87497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87332</t>
+          <t>87497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86201</t>
+          <t>85762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86201</t>
+          <t>85762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78460</t>
+          <t>77360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78460</t>
+          <t>77360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7323,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>27244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>27244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>52808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>52808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -7479,12 +7479,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>57708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>89355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>57708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>89355</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97451</t>
+          <t>97641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>133256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97451</t>
+          <t>97641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>133256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75842</t>
+          <t>76423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106962</t>
+          <t>110127</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75842</t>
+          <t>76423</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106962</t>
+          <t>110127</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -7951,12 +7951,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80111</t>
+          <t>79399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80111</t>
+          <t>79399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>91315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>91315</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129420</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153189</t>
+          <t>155660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196065</t>
+          <t>200846</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153189</t>
+          <t>155660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196065</t>
+          <t>200846</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70382</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>106952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70382</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>106952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>164184</t>
+          <t>166473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>211541</t>
+          <t>213611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>164184</t>
+          <t>166473</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>211541</t>
+          <t>213611</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>201733</t>
+          <t>202933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>251342</t>
+          <t>247463</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>201733</t>
+          <t>202933</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>251342</t>
+          <t>247463</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76346</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>114479</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>114479</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -8739,12 +8739,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66919</t>
+          <t>66554</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66919</t>
+          <t>66554</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>387784</t>
+          <t>387006</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>466161</t>
+          <t>464203</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>387784</t>
+          <t>387006</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>466161</t>
+          <t>464203</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>662790</t>
+          <t>660477</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>743566</t>
+          <t>745513</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>662790</t>
+          <t>660477</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>743566</t>
+          <t>745513</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>378553</t>
+          <t>375339</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>447972</t>
+          <t>446932</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>378553</t>
+          <t>375339</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>447972</t>
+          <t>446932</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>182789</t>
+          <t>183112</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>238906</t>
+          <t>241394</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>182789</t>
+          <t>183112</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>238906</t>
+          <t>241394</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -9461,32 +9461,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46179</t>
+          <t>47954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9496,32 +9496,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46179</t>
+          <t>47954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -9539,32 +9539,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>70817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>80993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9574,32 +9574,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>70817</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>80993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -9617,32 +9617,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58813</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>55835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>77418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9652,32 +9652,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58813</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>55835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>77418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -9695,32 +9695,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9730,32 +9730,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -9773,17 +9773,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9808,17 +9808,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>208556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9855,32 +9855,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9890,32 +9890,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -9933,32 +9933,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9968,32 +9968,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -10011,32 +10011,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>47286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>67555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>47286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>67555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10202,17 +10202,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>182210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10249,32 +10249,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10284,32 +10284,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -10327,32 +10327,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10362,32 +10362,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -10405,32 +10405,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10440,32 +10440,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -10483,32 +10483,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10518,32 +10518,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -10561,17 +10561,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10596,17 +10596,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10643,32 +10643,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>71659</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130938</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10678,32 +10678,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71659</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130938</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -10721,32 +10721,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>300957</t>
+          <t>105600</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160505</t>
+          <t>92909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>425119</t>
+          <t>118413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10756,32 +10756,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>300957</t>
+          <t>105600</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160505</t>
+          <t>92909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>425119</t>
+          <t>118413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -10799,32 +10799,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>63582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>87472</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10834,32 +10834,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>63582</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>87472</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -10877,32 +10877,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72717</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10912,32 +10912,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72717</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -10955,17 +10955,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>480394</t>
+          <t>300174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155933</t>
+          <t>132556</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>120529</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221625</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155933</t>
+          <t>132556</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>120529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221625</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -11115,32 +11115,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>105035</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>91604</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111699</t>
+          <t>119227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>105035</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>91604</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111699</t>
+          <t>119227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>72293</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>61902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79929</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>72293</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>61902</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79929</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -11271,32 +11271,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>30887</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11306,32 +11306,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>30887</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -11349,17 +11349,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11384,17 +11384,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>355376</t>
+          <t>349155</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -11431,32 +11431,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>146301</t>
+          <t>155679</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>133017</t>
+          <t>142220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158644</t>
+          <t>170469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11466,32 +11466,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>146301</t>
+          <t>155679</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>133017</t>
+          <t>142220</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158644</t>
+          <t>170469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -11509,32 +11509,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>82090</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>76643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94059</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11544,32 +11544,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82090</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>76643</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94059</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -11587,32 +11587,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52495</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11622,32 +11622,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52495</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -11665,32 +11665,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11700,32 +11700,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11778,17 +11778,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>307795</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11825,32 +11825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>473350</t>
+          <t>472234</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>297629</t>
+          <t>443070</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>567808</t>
+          <t>499056</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11860,32 +11860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>473350</t>
+          <t>472234</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>297629</t>
+          <t>443070</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>567808</t>
+          <t>499056</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -11903,32 +11903,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>613059</t>
+          <t>449794</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>456290</t>
+          <t>423542</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>960889</t>
+          <t>476629</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -11938,32 +11938,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>613059</t>
+          <t>449794</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>456290</t>
+          <t>423542</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>960889</t>
+          <t>476629</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -11981,32 +11981,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>334170</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>188542</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>358840</t>
+          <t>359665</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12016,32 +12016,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>334170</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>188542</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>358840</t>
+          <t>359665</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -12059,32 +12059,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>160391</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>101605</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>192178</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12094,32 +12094,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>160391</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>101605</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>192178</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -12137,17 +12137,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12172,17 +12172,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1550349</t>
+          <t>1429909</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
